--- a/tests/data/clamped/Book5.xlsx
+++ b/tests/data/clamped/Book5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Documents/nuh-helper/tests/data/clamped/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC5F14E-BA48-9242-B11E-F5757B357A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB7CE61-5B8E-7640-9C6B-ECA54FD4422C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="22200" windowWidth="21980" windowHeight="12560" activeTab="1" xr2:uid="{03BDD79C-C6BF-7644-AFA3-5ACD5002720F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>ptid</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>zuul</t>
+  </si>
+  <si>
+    <t>shoes</t>
   </si>
 </sst>
 </file>
@@ -476,9 +479,6 @@
       <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -486,6 +486,9 @@
       </c>
       <c r="B2" t="s">
         <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -569,8 +572,8 @@
         <v>45907</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="1">
-        <v>46557</v>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
